--- a/PLANILHA CARDAPIO E BAIRROS EDUARDO.xlsx
+++ b/PLANILHA CARDAPIO E BAIRROS EDUARDO.xlsx
@@ -2373,8 +2373,19 @@
       <c r="F50" s="7" t="n"/>
     </row>
     <row r="51" ht="15" customHeight="1">
-      <c r="A51" s="9" t="n"/>
-      <c r="B51" s="10" t="n"/>
+      <c r="A51" s="9" t="inlineStr">
+        <is>
+          <t>Nova Porto Velho</t>
+        </is>
+      </c>
+      <c r="B51" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>nova pvh</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.787401575" bottom="0.787401575" header="0.31496062" footer="0.31496062"/>
